--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718BA9DA-D8BB-4CFF-B402-BB068FDA0E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232EBEEF-94AB-4B1E-9AF9-2A609712F5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="60">
   <si>
     <t>Id</t>
   </si>
@@ -54,174 +54,209 @@
     <t>名称</t>
   </si>
   <si>
+    <t>图片</t>
+  </si>
+  <si>
+    <t>攻击+</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":6}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":2,"Value":8}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strike_ironclad</t>
+  </si>
+  <si>
+    <t>defend_ironclad</t>
+  </si>
+  <si>
+    <t>痛击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>痛击+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":9}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":10},{"EffectId":5,"Value":3}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":8},{"EffectId":5,"Value":2}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpgradeId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardEffectEntry[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑柄打击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑柄打击+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":9},{"EffectId":3,"Value":1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":10},{"EffectId":3,"Value":2}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pommel_strike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrug_it_off</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>耸肩无视</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":2,"Value":8},{"EffectId":3,"Value":1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":2,"Value":11},{"EffectId":3,"Value":1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blood_wall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":6,"Value":2},{"EffectId":2,"Value":16}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":6,"Value":2},{"EffectId":2,"Value":20}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron_wave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defend_ironclad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁斩波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":2,"Value":5},{"EffectId":1,"Value":5}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":2,"Value":7},{"EffectId":1,"Value":7}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slimed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黏液</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":3,"Value":1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardTrait</t>
+  </si>
+  <si>
+    <t>特性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>费用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>效果</t>
-  </si>
-  <si>
-    <t>图片</t>
-  </si>
-  <si>
-    <t>攻击+</t>
-  </si>
-  <si>
-    <t>防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"EffectId":2,"Value":5}]</t>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":6}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":2,"Value":8}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>strike_ironclad</t>
-  </si>
-  <si>
-    <t>defend_ironclad</t>
-  </si>
-  <si>
-    <t>痛击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>痛击+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":9}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":10},{"EffectId":5,"Value":3}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":8},{"EffectId":5,"Value":2}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UpgradeId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强化id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CardEffectEntry[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>剑柄打击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>剑柄打击+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":9},{"EffectId":3,"Value":1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":10},{"EffectId":3,"Value":2}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pommel_strike</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shrug_it_off</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>耸肩无视</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":2,"Value":8},{"EffectId":3,"Value":1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":2,"Value":11},{"EffectId":3,"Value":1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>blood_wall</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>血墙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":6,"Value":2},{"EffectId":2,"Value":16}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":6,"Value":2},{"EffectId":2,"Value":20}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iron_wave</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>defend_ironclad</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁斩波</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":2,"Value":5},{"EffectId":1,"Value":5}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":2,"Value":7},{"EffectId":1,"Value":7}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exhaust</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -762,19 +797,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="6" max="6" width="64.6640625" customWidth="1"/>
+    <col min="7" max="7" width="64.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -785,14 +820,17 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -808,397 +846,466 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="G3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5">
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>33</v>
+      <c r="E6" t="s">
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
+        <v>57</v>
+      </c>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="1">
+        <v>44</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7">
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="1">
-        <v>2</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8">
+      <c r="H8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="1">
+        <v>17</v>
+      </c>
+      <c r="D9">
         <v>2</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9">
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10">
+      <c r="H10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11">
+      <c r="H11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="1">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12">
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12">
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="1">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13">
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="1">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14">
         <v>2</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14">
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="1">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15">
         <v>2</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15">
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16">
+      <c r="H16" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D18">
         <v>1</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="1" t="s">
+      <c r="E18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" t="s">
         <v>51</v>
       </c>
-      <c r="G17">
+      <c r="H18" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232EBEEF-94AB-4B1E-9AF9-2A609712F5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBBE451-6114-4894-9B14-B2AA352F8DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="61">
   <si>
     <t>Id</t>
   </si>
@@ -221,42 +221,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>status</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"EffectId":3,"Value":1}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>特性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>费用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":2,"Value":5}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exhaust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>CardTrait</t>
-  </si>
-  <si>
-    <t>特性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>费用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":2,"Value":5}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exhaust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Traits</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -820,8 +825,8 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
-        <v>52</v>
+      <c r="F1" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="G1" t="s">
         <v>11</v>
@@ -846,8 +851,8 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
-        <v>52</v>
+      <c r="F2" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="G2" t="s">
         <v>23</v>
@@ -867,16 +872,16 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
         <v>54</v>
-      </c>
-      <c r="E3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" t="s">
-        <v>56</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>22</v>
@@ -899,7 +904,7 @@
         <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
@@ -925,7 +930,7 @@
         <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
@@ -951,10 +956,10 @@
         <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -977,7 +982,7 @@
         <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -1003,7 +1008,7 @@
         <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
         <v>20</v>
@@ -1029,7 +1034,7 @@
         <v>28</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -1055,7 +1060,7 @@
         <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
         <v>30</v>
@@ -1081,7 +1086,7 @@
         <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
         <v>31</v>
@@ -1107,7 +1112,7 @@
         <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
         <v>35</v>
@@ -1133,7 +1138,7 @@
         <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
         <v>36</v>
@@ -1159,7 +1164,7 @@
         <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G14" t="s">
         <v>39</v>
@@ -1185,7 +1190,7 @@
         <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
         <v>40</v>
@@ -1211,7 +1216,7 @@
         <v>28</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
         <v>46</v>
@@ -1237,7 +1242,7 @@
         <v>28</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G17" t="s">
         <v>47</v>
@@ -1259,14 +1264,14 @@
       <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" t="s">
         <v>50</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18" t="s">
-        <v>51</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
